--- a/web/logs/20260309_230127_42/metrics.xlsx
+++ b/web/logs/20260309_230127_42/metrics.xlsx
@@ -19,6 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="wolf_survival_days_by_model" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="wolf_elim_rate_by_model" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="good_id_hit_rate_by_model" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="belief_dev_rate" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="belief_dev_rate_seat" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1034,6 +1036,203 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>metrics_seed_42</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.4189723320158103</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>metrics_seed_42</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.4102564102564102</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>metrics_seed_42</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.46875</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>metrics_seed_42</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>metrics_seed_42</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4571428571428571</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>metrics_seed_42</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5517241379310345</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>metrics_seed_42</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1515151515151515</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>metrics_seed_42</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5277777777777778</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metrics_seed_42</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
